--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6865-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6865-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D85684C-509B-431E-83F8-729E770A93E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCCB06B2-6716-4188-BED4-1FBC94C47E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{C4014B7A-522F-4FB2-A47B-BC536A966BF7}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{617D08F4-FEF8-4FC3-A7FA-DA04CCDDF245}"/>
   </bookViews>
   <sheets>
     <sheet name="6865-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1457,19 +1457,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E75B417F-9A8F-46C0-A475-E1614E315925}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{868C32B6-814D-432E-BFE1-B38884CF4118}">
   <dimension ref="A1:X10"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="9" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1503,7 +1501,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1539,7 +1537,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1591,7 +1589,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1659,7 +1657,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1731,7 +1729,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37"/>
       <c r="B6" s="38"/>
       <c r="C6" s="13" t="s">
@@ -1759,7 +1757,7 @@
       <c r="W6" s="44"/>
       <c r="X6" s="40"/>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="45">
         <v>2023</v>
       </c>
@@ -1831,7 +1829,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="47">
         <v>2022</v>
       </c>
@@ -1903,7 +1901,7 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="45">
         <v>2021</v>
       </c>
@@ -1975,7 +1973,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>33</v>
       </c>
